--- a/VerveStacks_GBR/source_data/VerveStacks_GBR.xlsx
+++ b/VerveStacks_GBR/source_data/VerveStacks_GBR.xlsx
@@ -8,16 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\VerveStacks\output\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3C92CE96-B870-4A65-8F4D-448C3CD2F2F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A9A4F946-E1E7-413B-870A-A882CCB66386}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="weo_pg" sheetId="22" r:id="rId1"/>
-    <sheet name="re_targets" sheetId="21" r:id="rId2"/>
-    <sheet name="ccs_retrofits" sheetId="20" r:id="rId3"/>
-    <sheet name="Calibration" sheetId="19" r:id="rId4"/>
-    <sheet name="existing_stock" sheetId="18" r:id="rId5"/>
+    <sheet name="weo_pg" sheetId="27" r:id="rId1"/>
+    <sheet name="re_targets" sheetId="26" r:id="rId2"/>
+    <sheet name="ccs_retrofits" sheetId="25" r:id="rId3"/>
+    <sheet name="Calibration" sheetId="24" r:id="rId4"/>
+    <sheet name="existing_stock" sheetId="23" r:id="rId5"/>
     <sheet name="historical_data_long" sheetId="14" r:id="rId6"/>
     <sheet name="iamc_data" sheetId="11" r:id="rId7"/>
     <sheet name="iamc_charts" sheetId="10" r:id="rId8"/>
@@ -4368,7 +4368,7 @@
         <xdr:cNvPr id="3" name="Picture 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F881CEAD-5240-357B-ECA2-BA0BBCCA4EF3}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0B07969C-B780-3831-A733-E318E75A29B2}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4423,7 +4423,7 @@
         <xdr:cNvPr id="3" name="Picture 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{379AD11A-CA4D-2697-96FE-65CD4FF1EF6A}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{08D1FFC3-FF10-1E52-60DB-FD2380DD83A1}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4829,7 +4829,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04B5C38D-D030-4DBA-BB41-EF5A1C4D63B2}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D456E0F8-D9A4-42A1-86BD-8AE15FF02813}">
   <dimension ref="B2:I129"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -14555,7 +14555,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4BC8AB97-7B0E-43A1-8569-764C94B6484B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9314D6FE-4690-411B-91BC-2A9D54069515}">
   <dimension ref="B2:L72"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -17005,7 +17005,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{55389BAD-E739-4E38-B3C9-0BA57D3FD3AE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{45D3C342-8BDB-42C0-AAA2-1685AE4C794E}">
   <dimension ref="B2:J150"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -21312,7 +21312,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2B5171D8-A566-4AD2-8355-F8BBE7062C4C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EAD0148D-AC1C-40D6-AEF3-ED695CED867E}">
   <dimension ref="A1:H41"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -21953,7 +21953,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E3A41E66-3E92-4B22-9796-040E374F4E2F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9AE9C563-D6DF-4791-9F5A-9BDF699F2384}">
   <dimension ref="A1:Y882"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -49776,7 +49776,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="Q544">
-        <v>0.55373821771400944</v>
+        <v>0.55373821771400933</v>
       </c>
     </row>
     <row r="545" spans="1:17" x14ac:dyDescent="0.45">
@@ -49811,7 +49811,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="Q545">
-        <v>0.55373821771400944</v>
+        <v>0.55373821771400933</v>
       </c>
     </row>
     <row r="546" spans="1:17" x14ac:dyDescent="0.45">
@@ -49846,7 +49846,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="Q546">
-        <v>0.55373821771400944</v>
+        <v>0.55373821771400933</v>
       </c>
     </row>
     <row r="547" spans="1:17" x14ac:dyDescent="0.45">

--- a/VerveStacks_GBR/source_data/VerveStacks_GBR.xlsx
+++ b/VerveStacks_GBR/source_data/VerveStacks_GBR.xlsx
@@ -8,16 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\VerveStacks\output\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A9A4F946-E1E7-413B-870A-A882CCB66386}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{ACEBA9D0-C5B2-4067-BD8A-01D6CE7CD758}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="weo_pg" sheetId="27" r:id="rId1"/>
-    <sheet name="re_targets" sheetId="26" r:id="rId2"/>
-    <sheet name="ccs_retrofits" sheetId="25" r:id="rId3"/>
-    <sheet name="Calibration" sheetId="24" r:id="rId4"/>
-    <sheet name="existing_stock" sheetId="23" r:id="rId5"/>
+    <sheet name="weo_pg" sheetId="32" r:id="rId1"/>
+    <sheet name="re_targets" sheetId="31" r:id="rId2"/>
+    <sheet name="ccs_retrofits" sheetId="30" r:id="rId3"/>
+    <sheet name="Calibration" sheetId="29" r:id="rId4"/>
+    <sheet name="existing_stock" sheetId="28" r:id="rId5"/>
     <sheet name="historical_data_long" sheetId="14" r:id="rId6"/>
     <sheet name="iamc_data" sheetId="11" r:id="rId7"/>
     <sheet name="iamc_charts" sheetId="10" r:id="rId8"/>
@@ -4368,7 +4368,7 @@
         <xdr:cNvPr id="3" name="Picture 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0B07969C-B780-3831-A733-E318E75A29B2}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B16DC362-A2A2-9E57-03B5-A8FF2B323B59}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4423,7 +4423,7 @@
         <xdr:cNvPr id="3" name="Picture 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{08D1FFC3-FF10-1E52-60DB-FD2380DD83A1}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BF271AE6-A758-971A-1820-C9C1AF9B15AF}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4829,7 +4829,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D456E0F8-D9A4-42A1-86BD-8AE15FF02813}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EBA36297-CF96-41AF-9E36-FD6D77A6D173}">
   <dimension ref="B2:I129"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -14555,7 +14555,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9314D6FE-4690-411B-91BC-2A9D54069515}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2814C3B8-A42B-4FAC-A71F-7C46EBE4673E}">
   <dimension ref="B2:L72"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -17005,7 +17005,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{45D3C342-8BDB-42C0-AAA2-1685AE4C794E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5F161947-E640-4293-A2F1-C231DF6B681C}">
   <dimension ref="B2:J150"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -21312,7 +21312,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EAD0148D-AC1C-40D6-AEF3-ED695CED867E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E986258F-FF02-4B86-A15F-49DE1CCBF48F}">
   <dimension ref="A1:H41"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -21953,7 +21953,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9AE9C563-D6DF-4791-9F5A-9BDF699F2384}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{44D19731-19DA-4F89-95F0-CEFCF8CDEC7D}">
   <dimension ref="A1:Y882"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -41059,7 +41059,7 @@
         <v>235</v>
       </c>
       <c r="B360" t="s">
-        <v>911</v>
+        <v>909</v>
       </c>
       <c r="C360" t="s">
         <v>88</v>
@@ -41071,25 +41071,25 @@
         <v>2024</v>
       </c>
       <c r="I360" t="s">
-        <v>912</v>
+        <v>910</v>
       </c>
       <c r="J360" t="s">
         <v>480</v>
       </c>
       <c r="L360">
-        <v>2.07E-2</v>
+        <v>8.1200000000000008E-2</v>
       </c>
       <c r="M360">
-        <v>1633.5000000000002</v>
+        <v>1633.5</v>
       </c>
       <c r="N360">
-        <v>64.350000000000009</v>
+        <v>64.349999999999994</v>
       </c>
       <c r="O360">
-        <v>8.19</v>
+        <v>8.1899999999999977</v>
       </c>
       <c r="P360">
-        <v>0.37080000000000002</v>
+        <v>0.37079999999999996</v>
       </c>
       <c r="R360">
         <v>35</v>
@@ -41121,7 +41121,7 @@
         <v>235</v>
       </c>
       <c r="B361" t="s">
-        <v>909</v>
+        <v>911</v>
       </c>
       <c r="C361" t="s">
         <v>88</v>
@@ -41133,25 +41133,25 @@
         <v>2024</v>
       </c>
       <c r="I361" t="s">
-        <v>910</v>
+        <v>912</v>
       </c>
       <c r="J361" t="s">
         <v>480</v>
       </c>
       <c r="L361">
-        <v>8.1200000000000008E-2</v>
+        <v>2.07E-2</v>
       </c>
       <c r="M361">
-        <v>1633.5</v>
+        <v>1633.5000000000002</v>
       </c>
       <c r="N361">
-        <v>64.349999999999994</v>
+        <v>64.350000000000009</v>
       </c>
       <c r="O361">
-        <v>8.1899999999999977</v>
+        <v>8.19</v>
       </c>
       <c r="P361">
-        <v>0.37079999999999996</v>
+        <v>0.37080000000000002</v>
       </c>
       <c r="R361">
         <v>35</v>
@@ -49776,7 +49776,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="Q544">
-        <v>0.55373821771400933</v>
+        <v>0.55373821771400944</v>
       </c>
     </row>
     <row r="545" spans="1:17" x14ac:dyDescent="0.45">
@@ -49811,7 +49811,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="Q545">
-        <v>0.55373821771400933</v>
+        <v>0.55373821771400944</v>
       </c>
     </row>
     <row r="546" spans="1:17" x14ac:dyDescent="0.45">
@@ -49846,7 +49846,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="Q546">
-        <v>0.55373821771400933</v>
+        <v>0.55373821771400944</v>
       </c>
     </row>
     <row r="547" spans="1:17" x14ac:dyDescent="0.45">
